--- a/data/ams_weekly_data/Audio_Array/ads_report_week16.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week16.xlsx
@@ -12579,7 +12579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12774,19 +12774,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42297</v>
+        <v>34615</v>
       </c>
       <c r="E6" t="n">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="F6" t="n">
-        <v>5682.34</v>
+        <v>4650.283759216506</v>
       </c>
       <c r="G6" t="n">
-        <v>11179.67</v>
+        <v>9149.16</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -12798,28 +12798,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16031.33333333333</v>
+        <v>7682</v>
       </c>
       <c r="E7" t="n">
-        <v>114.3333333333333</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>856.6466666666666</v>
+        <v>1032.056240783494</v>
       </c>
       <c r="G7" t="n">
-        <v>4882.476666666666</v>
+        <v>2030.51</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -12840,19 +12840,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16031.33333333333</v>
+        <v>31912</v>
       </c>
       <c r="E8" t="n">
-        <v>114.3333333333333</v>
+        <v>228</v>
       </c>
       <c r="F8" t="n">
-        <v>856.6466666666666</v>
+        <v>1705.232211182743</v>
       </c>
       <c r="G8" t="n">
-        <v>4882.476666666666</v>
+        <v>9719.008788938434</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -12873,16 +12873,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16031.33333333333</v>
+        <v>16182</v>
       </c>
       <c r="E9" t="n">
-        <v>114.3333333333333</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>856.6466666666666</v>
+        <v>864.7077888172573</v>
       </c>
       <c r="G9" t="n">
-        <v>4882.476666666666</v>
+        <v>4928.421211061565</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
@@ -12906,19 +12906,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74590</v>
+        <v>33186</v>
       </c>
       <c r="E10" t="n">
-        <v>605</v>
+        <v>232</v>
       </c>
       <c r="F10" t="n">
-        <v>8036.23</v>
+        <v>3064.238396304979</v>
       </c>
       <c r="G10" t="n">
-        <v>26606.77</v>
+        <v>8303.380000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -12930,28 +12930,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42879</v>
+        <v>19168</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F11" t="n">
-        <v>3486.77</v>
+        <v>2301.831213342371</v>
       </c>
       <c r="G11" t="n">
-        <v>21605.95</v>
+        <v>8473.730000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -12963,28 +12963,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22737</v>
+        <v>22235</v>
       </c>
       <c r="E12" t="n">
-        <v>251</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>1510.99</v>
+        <v>2670.160390352651</v>
       </c>
       <c r="G12" t="n">
-        <v>38131.35000000001</v>
+        <v>9829.660000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -12996,28 +12996,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32375.66666666667</v>
+        <v>42879</v>
       </c>
       <c r="E13" t="n">
-        <v>136.6666666666667</v>
+        <v>165</v>
       </c>
       <c r="F13" t="n">
-        <v>1438.91</v>
+        <v>3486.77</v>
       </c>
       <c r="G13" t="n">
-        <v>2851.98</v>
+        <v>21605.95</v>
       </c>
       <c r="H13" t="n">
-        <v>1.333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -13029,28 +13029,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32375.66666666667</v>
+        <v>22737</v>
       </c>
       <c r="E14" t="n">
-        <v>136.6666666666667</v>
+        <v>251</v>
       </c>
       <c r="F14" t="n">
-        <v>1438.91</v>
+        <v>1510.99</v>
       </c>
       <c r="G14" t="n">
-        <v>2851.98</v>
+        <v>38131.35000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -13067,23 +13067,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32375.66666666667</v>
+        <v>51931</v>
       </c>
       <c r="E15" t="n">
-        <v>136.6666666666667</v>
+        <v>219</v>
       </c>
       <c r="F15" t="n">
-        <v>1438.91</v>
+        <v>2308.013698483158</v>
       </c>
       <c r="G15" t="n">
-        <v>2851.98</v>
+        <v>4574.58</v>
       </c>
       <c r="H15" t="n">
-        <v>1.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13095,28 +13095,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6503.962962962963</v>
+        <v>21155</v>
       </c>
       <c r="E16" t="n">
-        <v>32.22222222222222</v>
+        <v>89</v>
       </c>
       <c r="F16" t="n">
-        <v>496.7011111111111</v>
+        <v>940.2222735082293</v>
       </c>
       <c r="G16" t="n">
-        <v>1457.093333333333</v>
+        <v>1863.56</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8518518518518519</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -13128,28 +13128,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6503.962962962963</v>
+        <v>24041</v>
       </c>
       <c r="E17" t="n">
-        <v>32.22222222222222</v>
+        <v>101</v>
       </c>
       <c r="F17" t="n">
-        <v>496.7011111111111</v>
+        <v>1068.494028008611</v>
       </c>
       <c r="G17" t="n">
-        <v>1457.093333333333</v>
+        <v>2117.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8518518518518519</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -13166,23 +13166,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6503.962962962963</v>
+        <v>29526</v>
       </c>
       <c r="E18" t="n">
-        <v>32.22222222222222</v>
+        <v>158</v>
       </c>
       <c r="F18" t="n">
-        <v>496.7011111111111</v>
+        <v>2590.132451264225</v>
       </c>
       <c r="G18" t="n">
-        <v>1457.093333333333</v>
+        <v>8197.787953153151</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8518518518518519</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -13199,23 +13199,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E19" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G19" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -13232,23 +13232,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E20" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G20" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -13265,23 +13265,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E21" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G21" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -13298,23 +13298,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6503.962962962963</v>
+        <v>10718</v>
       </c>
       <c r="E22" t="n">
-        <v>32.22222222222222</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>496.7011111111111</v>
+        <v>1499.953717453995</v>
       </c>
       <c r="G22" t="n">
-        <v>1457.093333333333</v>
+        <v>2879.66</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8518518518518519</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -13331,23 +13331,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E23" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G23" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -13364,23 +13364,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E24" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G24" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -13397,23 +13397,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E25" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G25" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -13430,23 +13430,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6503.962962962963</v>
+        <v>7235</v>
       </c>
       <c r="E26" t="n">
-        <v>32.22222222222222</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
-        <v>496.7011111111111</v>
+        <v>1076.939585399792</v>
       </c>
       <c r="G26" t="n">
-        <v>1457.093333333333</v>
+        <v>4146.610000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8518518518518519</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -13463,23 +13463,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E27" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G27" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -13496,23 +13496,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6503.962962962963</v>
+        <v>36846</v>
       </c>
       <c r="E28" t="n">
-        <v>32.22222222222222</v>
+        <v>157</v>
       </c>
       <c r="F28" t="n">
-        <v>496.7011111111111</v>
+        <v>1368.511571703016</v>
       </c>
       <c r="G28" t="n">
-        <v>1457.093333333333</v>
+        <v>12620.85204684685</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8518518518518519</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -13529,23 +13529,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E29" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G29" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -13562,23 +13562,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6503.962962962963</v>
+        <v>6154</v>
       </c>
       <c r="E30" t="n">
-        <v>32.22222222222222</v>
+        <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>496.7011111111111</v>
+        <v>872.4620912036225</v>
       </c>
       <c r="G30" t="n">
-        <v>1457.093333333333</v>
+        <v>3304.24</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8518518518518519</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13595,23 +13595,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E31" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G31" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13628,23 +13628,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E32" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G32" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -13661,23 +13661,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E33" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G33" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -13694,23 +13694,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E34" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G34" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -13727,23 +13727,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E35" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G35" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -13760,23 +13760,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6503.962962962963</v>
+        <v>20287</v>
       </c>
       <c r="E36" t="n">
-        <v>32.22222222222222</v>
+        <v>123</v>
       </c>
       <c r="F36" t="n">
-        <v>496.7011111111111</v>
+        <v>2453.216415080026</v>
       </c>
       <c r="G36" t="n">
-        <v>1457.093333333333</v>
+        <v>2982.2</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8518518518518519</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -13793,23 +13793,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6503.962962962963</v>
+        <v>12382</v>
       </c>
       <c r="E37" t="n">
-        <v>32.22222222222222</v>
+        <v>39</v>
       </c>
       <c r="F37" t="n">
-        <v>496.7011111111111</v>
+        <v>480.9685185185185</v>
       </c>
       <c r="G37" t="n">
-        <v>1457.093333333333</v>
+        <v>3219.49</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8518518518518519</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13826,23 +13826,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E38" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G38" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -13859,23 +13859,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E39" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G39" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -13892,23 +13892,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E40" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G40" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -13925,23 +13925,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6503.962962962963</v>
+        <v>1914</v>
       </c>
       <c r="E41" t="n">
-        <v>32.22222222222222</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>496.7011111111111</v>
+        <v>70.38851851851851</v>
       </c>
       <c r="G41" t="n">
-        <v>1457.093333333333</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8518518518518519</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -13958,25 +13958,157 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>B0FLYJFC22</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12264</v>
+      </c>
+      <c r="E42" t="n">
+        <v>78</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1590.586760487916</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1990.68</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1914</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>70.38851851851851</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1914</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>70.38851851851851</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1914</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>70.38851851851851</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>B0G4DNF8RZ</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>6503.962962962963</v>
-      </c>
-      <c r="E42" t="n">
-        <v>32.22222222222222</v>
-      </c>
-      <c r="F42" t="n">
-        <v>496.7011111111111</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1457.093333333333</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.8518518518518519</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="D46" t="n">
+        <v>1914</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>70.38851851851851</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week16.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week16.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
